--- a/data/game_data.xlsx
+++ b/data/game_data.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -144,8 +144,19 @@
       <color theme="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00E8D87C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00E8B870"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -243,8 +254,13 @@
         <fgColor rgb="00161E2A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003A2A10"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -320,11 +336,20 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -442,6 +467,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -807,35 +842,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="38" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>WEAPON BASE STATS  —  Edit yellow/green cells. Do not rename columns (game reads by header).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>WEAPON BASE STATS  —  Dark rows = current. Green = fill in. Amber = incomplete (needs values). Do not rename columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Weapon ID
-(no spaces)</t>
+(snake_case)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -846,7 +888,8 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Type
-ballistic/energy/missile</t>
+ballistic/energy
+missile/fire</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -857,56 +900,95 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>AOE Radius
+(0=none, 0–1 scale)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Burn %
+(of hit damage)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Burn Duration
+(seconds)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Split Count
+(0=none)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Split Trigger
+impact/expiry/bounce</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Child DMG %
+(of parent)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Child Spread
+(degrees)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>Fire Rate
 (sec between shots)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Bullet Speed
 (pixels/sec)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>DMG Scale
-(per tier, 0–1)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+(per tier)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Rate Scale
-(per tier, 0–1)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Colour R
-(0–1)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Colour G
-(0–1)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Colour B
-(0–1)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+(per tier)</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>R (0–1)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>G (0–1)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>B (0–1)</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Design Notes</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Used in weapons.json key</t>
+          <t>Used as key in weapons.json</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -926,46 +1008,77 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>Explosion radius on impact</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>e.g. 0.5 = 50% burn damage</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>How long DOT lasts</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Child projectiles spawned</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>When children spawn</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>e.g. 0.3 = 30% per child</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Fan angle for children</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>Lower = faster</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Typical 500–1100</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>e.g. 0.44 = +44% per tier</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>e.g. 0.16 = +16% per tier</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Bullet colour, red channel</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>For your reference only</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>e.g. 0.16 = faster per tier</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Bullet colour</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>ballistic</t>
+          <t>machine_gun</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Ballistic</t>
+          <t>Machine Gun</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -977,41 +1090,60 @@
         <v>10</v>
       </c>
       <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>0.44</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="P4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="R4" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>Fast, low damage. Yellow tracer.</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>energy_beam</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Energy Beam</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1023,33 +1155,52 @@
         <v>18</v>
       </c>
       <c r="E5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>1100</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>0.44</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="P5" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="Q5" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Mid damage, fastest bullet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>Mid damage, fastest bullet. Minor burn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>missile</t>
@@ -1069,117 +1220,458 @@
         <v>35</v>
       </c>
       <c r="E6" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>0.44</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Slow fire, heavy damage. Orange.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>Slow fire, heavy damage. Minor burn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>heavy_machine_gun</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Heavy Machine Gun</t>
+        </is>
+      </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
           <t>ballistic</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
+      <c r="D7" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Higher damage, slightly slower than MG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>homing_missile</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Homing Missile</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>Steers toward nearest enemy. Needs homing system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>napalm</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Napalm</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>Hits → applies burn DOT. Fire type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>nuke</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Nuke</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>Massive AOE + heavy burn. Slow fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>cluster_bomb</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Cluster Bomb</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>ballistic</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>Explodes into 10 child projectiles on impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>nano_bots</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>Nano Bots</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="7" t="n"/>
+      <c r="D12" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="44" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I12" s="44" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="J12" s="44" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="K12" s="44" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="L12" s="44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M12" s="44" t="n">
+        <v>900</v>
+      </c>
+      <c r="N12" s="44" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O12" s="44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P12" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S12" s="45" t="inlineStr">
+        <is>
+          <t>⚠ INCOMPLETE — fill in split values. Many scattered bots.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1276,7 +1768,7 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="17" t="n"/>
+      <c r="A4" s="46" t="n"/>
       <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Fire Rate</t>
@@ -1304,7 +1796,7 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="17" t="n"/>
+      <c r="A5" s="46" t="n"/>
       <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Projectiles</t>
@@ -1332,7 +1824,7 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="17" t="n"/>
+      <c r="A6" s="46" t="n"/>
       <c r="B6" s="18" t="inlineStr">
         <is>
           <t>AOE Radius</t>
@@ -1360,7 +1852,7 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="17" t="n"/>
+      <c r="A7" s="46" t="n"/>
       <c r="B7" s="11" t="inlineStr">
         <is>
           <t>DPS (dmg×rof×proj)</t>
@@ -1429,7 +1921,7 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="17" t="n"/>
+      <c r="A10" s="46" t="n"/>
       <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Fire Rate</t>
@@ -1457,7 +1949,7 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="17" t="n"/>
+      <c r="A11" s="46" t="n"/>
       <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Projectiles</t>
@@ -1485,7 +1977,7 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="17" t="n"/>
+      <c r="A12" s="46" t="n"/>
       <c r="B12" s="18" t="inlineStr">
         <is>
           <t>AOE Radius</t>
@@ -1513,7 +2005,7 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="17" t="n"/>
+      <c r="A13" s="46" t="n"/>
       <c r="B13" s="11" t="inlineStr">
         <is>
           <t>DPS (dmg×rof×proj)</t>
@@ -1582,7 +2074,7 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="17" t="n"/>
+      <c r="A16" s="46" t="n"/>
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Fire Rate</t>
@@ -1610,7 +2102,7 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="17" t="n"/>
+      <c r="A17" s="46" t="n"/>
       <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Projectiles</t>
@@ -1638,7 +2130,7 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="17" t="n"/>
+      <c r="A18" s="46" t="n"/>
       <c r="B18" s="18" t="inlineStr">
         <is>
           <t>AOE Radius</t>
@@ -1666,7 +2158,7 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="17" t="n"/>
+      <c r="A19" s="46" t="n"/>
       <c r="B19" s="11" t="inlineStr">
         <is>
           <t>DPS (dmg×rof×proj)</t>
@@ -1735,7 +2227,7 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="17" t="n"/>
+      <c r="A22" s="46" t="n"/>
       <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Fire Rate</t>
@@ -1763,7 +2255,7 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="17" t="n"/>
+      <c r="A23" s="46" t="n"/>
       <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Projectiles</t>
@@ -1791,7 +2283,7 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="17" t="n"/>
+      <c r="A24" s="46" t="n"/>
       <c r="B24" s="18" t="inlineStr">
         <is>
           <t>AOE Radius</t>
@@ -1819,7 +2311,7 @@
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="17" t="n"/>
+      <c r="A25" s="46" t="n"/>
       <c r="B25" s="11" t="inlineStr">
         <is>
           <t>DPS (dmg×rof×proj)</t>
@@ -1888,7 +2380,7 @@
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="17" t="n"/>
+      <c r="A28" s="46" t="n"/>
       <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Fire Rate</t>
@@ -1916,7 +2408,7 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="17" t="n"/>
+      <c r="A29" s="46" t="n"/>
       <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Projectiles</t>
@@ -1944,7 +2436,7 @@
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="17" t="n"/>
+      <c r="A30" s="46" t="n"/>
       <c r="B30" s="18" t="inlineStr">
         <is>
           <t>AOE Radius</t>
@@ -1972,7 +2464,7 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="17" t="n"/>
+      <c r="A31" s="46" t="n"/>
       <c r="B31" s="11" t="inlineStr">
         <is>
           <t>DPS (dmg×rof×proj)</t>
@@ -5721,7 +6213,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="38" t="inlineStr">
         <is>

--- a/data/game_data.xlsx
+++ b/data/game_data.xlsx
@@ -349,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -477,6 +477,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1622,50 +1628,46 @@
       <c r="G12" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="44" t="inlineStr">
+      <c r="H12" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" s="47" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="J12" s="47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K12" s="44" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="I12" s="44" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="J12" s="44" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="K12" s="44" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="L12" s="44" t="n">
+      <c r="L12" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="M12" s="44" t="n">
+      <c r="M12" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="N12" s="44" t="n">
+      <c r="N12" s="4" t="n">
         <v>0.44</v>
       </c>
-      <c r="O12" s="44" t="n">
+      <c r="O12" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="P12" s="44" t="n">
+      <c r="P12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="44" t="n">
+      <c r="Q12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R12" s="44" t="n">
+      <c r="R12" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="S12" s="45" t="inlineStr">
-        <is>
-          <t>⚠ INCOMPLETE — fill in split values. Many scattered bots.</t>
+      <c r="S12" s="48" t="inlineStr">
+        <is>
+          <t>20 bots spawn on impact, each with independent base dmg 6 (child_dmg_pct = bonus on top). Weapon merging in Pilot Academy makes these scale fast.</t>
         </is>
       </c>
     </row>
